--- a/docs/collections/shelley/metadata/data.xlsx
+++ b/docs/collections/shelley/metadata/data.xlsx
@@ -751,7 +751,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Two letters by Richard Garnett to Rinkichi Tsuchii. Letter 2</t>
+          <t>Fragment of an Address to the Jews</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -765,11 +765,19 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>On Zionism|Restoration of the Jews|A manuscript, written in his own hand</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>also known as "On Zionism" and "Restoration of the Jews"|A title of General Library's card catalog: [A manuscript, written in his own hand]|The third image is a transmitted light photograph to capture the watermark. According to Professor Nora Crook, a dolphin with the letters "ANT.FORTI C." is depicted.</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Garnett, Richard</t>
+          <t>Shelley, Percy Bysshe</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -777,40 +785,36 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b1499d0d-920a-413f-8616-66daa1c21e8f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e3e3be43-358d-47bf-a245-d52ffe4ed866.json</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>b1499d0d-920a-413f-8616-66daa1c21e8f</t>
+          <t>e3e3be43-358d-47bf-a245-d52ffe4ed866</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shelly/document/b1499d0d-920a-413f-8616-66daa1c21e8f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shelly/document/e3e3be43-358d-47bf-a245-d52ffe4ed866</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shelly/page/reuse</t>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4490ffbc84de3b218df00e8e55f729da534a6f4c.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b21f88051663fd540a6d382183349894d16b58b8.jpg</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22133</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>東京大学総合図書館 General Library in the University of Tokyo, JAPAN</t>
-        </is>
-      </c>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22131</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
@@ -822,7 +826,7 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b1499d0d-920a-413f-8616-66daa1c21e8f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e3e3be43-358d-47bf-a245-d52ffe4ed866/manifest</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -830,13 +834,13 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fragment of an Address to the Jews</t>
+          <t>Two letters by Richard Garnett to Rinkichi Tsuchii. Letter 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -850,19 +854,11 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>On Zionism|Restoration of the Jews|A manuscript, written in his own hand</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>also known as "On Zionism" and "Restoration of the Jews"|A title of General Library's card catalog: [A manuscript, written in his own hand]|The third image is a transmitted light photograph to capture the watermark. According to Professor Nora Crook, a dolphin with the letters "ANT.FORTI C." is depicted.</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Shelley, Percy Bysshe</t>
+          <t>Garnett, Richard</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -870,36 +866,40 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e3e3be43-358d-47bf-a245-d52ffe4ed866.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6f0c1352-3e7e-4bf0-90e9-eb360be55cf9.json</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>e3e3be43-358d-47bf-a245-d52ffe4ed866</t>
+          <t>6f0c1352-3e7e-4bf0-90e9-eb360be55cf9</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shelly/document/e3e3be43-358d-47bf-a245-d52ffe4ed866</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shelly/document/6f0c1352-3e7e-4bf0-90e9-eb360be55cf9</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shelly/page/reuse</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b21f88051663fd540a6d382183349894d16b58b8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0a1f57425b52b938db97ab87f5e4791ddef4deae.jpg</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22131</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22132</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library in the University of Tokyo, JAPAN</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
@@ -911,7 +911,7 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e3e3be43-358d-47bf-a245-d52ffe4ed866/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6f0c1352-3e7e-4bf0-90e9-eb360be55cf9/manifest</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -919,13 +919,13 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Two letters by Richard Garnett to Rinkichi Tsuchii. Letter 1</t>
+          <t>Two letters by Richard Garnett to Rinkichi Tsuchii. Letter 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -951,18 +951,18 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6f0c1352-3e7e-4bf0-90e9-eb360be55cf9.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b1499d0d-920a-413f-8616-66daa1c21e8f.json</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6f0c1352-3e7e-4bf0-90e9-eb360be55cf9</t>
+          <t>b1499d0d-920a-413f-8616-66daa1c21e8f</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shelly/document/6f0c1352-3e7e-4bf0-90e9-eb360be55cf9</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shelly/document/b1499d0d-920a-413f-8616-66daa1c21e8f</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0a1f57425b52b938db97ab87f5e4791ddef4deae.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4490ffbc84de3b218df00e8e55f729da534a6f4c.jpg</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22132</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/22133</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -996,7 +996,7 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6f0c1352-3e7e-4bf0-90e9-eb360be55cf9/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b1499d0d-920a-413f-8616-66daa1c21e8f/manifest</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
